--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3293-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3293-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DB56BAC-93E2-48F3-BDE8-36E0C4F78785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE60CFA8-84F2-41F1-8A33-4F22E36E5994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D033EC7A-EEE5-4E69-B221-CA64BC0D700F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{FE7CEE35-3009-47E4-97C6-DF57F9F46871}"/>
   </bookViews>
   <sheets>
     <sheet name="3293-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1508,26 +1508,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D74BC67-866C-481D-8F6B-F9F5A54A1088}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A64AA3A-53C7-4325-B930-2FB75B087F26}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="8.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1561,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1717,7 +1717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2022</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2021</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2020</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2019</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2018</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2017</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2016</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2015</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2014</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2013</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2012</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2011</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2010</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2009</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2008</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2007</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2006</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2005</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2004</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2003</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38" t="s">
         <v>56</v>
       </c>
